--- a/results.xlsx
+++ b/results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Desktop/Fantasy Cycling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="6_{791E1E6D-5D1E-411A-AA39-81A4A2AEEE1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{646BD413-8109-43DB-ADB2-276ED2D3E26F}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="6_{791E1E6D-5D1E-411A-AA39-81A4A2AEEE1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0002310A-C130-4D5A-9322-979BD1AC058D}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{D48BDCD1-ADE3-4EE7-A9DB-3C7F51FF7246}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D48BDCD1-ADE3-4EE7-A9DB-3C7F51FF7246}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="173">
   <si>
     <t>Stage 1</t>
   </si>
@@ -516,6 +516,48 @@
   </si>
   <si>
     <t>Florian Lipowitz</t>
+  </si>
+  <si>
+    <t>Stage 6</t>
+  </si>
+  <si>
+    <t>T. H. Johannessen</t>
+  </si>
+  <si>
+    <t>David Gaudu</t>
+  </si>
+  <si>
+    <t>Michael Storer</t>
+  </si>
+  <si>
+    <t>Stage 7</t>
+  </si>
+  <si>
+    <t>Volta ao Algarve</t>
+  </si>
+  <si>
+    <t>T. T. Teutenberg</t>
+  </si>
+  <si>
+    <t>Hugo Hofstetter</t>
+  </si>
+  <si>
+    <t>Luca Mozzato</t>
+  </si>
+  <si>
+    <t>Noah Hobbs</t>
+  </si>
+  <si>
+    <t>Santiago Mesa</t>
+  </si>
+  <si>
+    <t>Matteo Moschetti</t>
+  </si>
+  <si>
+    <t>Jarno Widar</t>
+  </si>
+  <si>
+    <t>Dylan van Baarle</t>
   </si>
 </sst>
 </file>
@@ -894,23 +936,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6820EB03-3F7F-49BA-9E92-28FA32BF7E1D}">
-  <dimension ref="A1:M21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.5546875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>42</v>
       </c>
@@ -951,7 +993,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>46042</v>
       </c>
@@ -992,7 +1034,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>46043</v>
       </c>
@@ -1033,7 +1075,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>46044</v>
       </c>
@@ -1074,7 +1116,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>46045</v>
       </c>
@@ -1115,7 +1157,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>46046</v>
       </c>
@@ -1156,7 +1198,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>46047</v>
       </c>
@@ -1197,7 +1239,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>46054</v>
       </c>
@@ -1238,7 +1280,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>46057</v>
       </c>
@@ -1279,7 +1321,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>46058</v>
       </c>
@@ -1320,7 +1362,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>46059</v>
       </c>
@@ -1361,7 +1403,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>46060</v>
       </c>
@@ -1402,7 +1444,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>46061</v>
       </c>
@@ -1443,7 +1485,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>46069</v>
       </c>
@@ -1484,7 +1526,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>46070</v>
       </c>
@@ -1525,7 +1567,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>46071</v>
       </c>
@@ -1566,7 +1608,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>46071</v>
       </c>
@@ -1607,7 +1649,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>46072</v>
       </c>
@@ -1648,7 +1690,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>46072</v>
       </c>
@@ -1689,7 +1731,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>46073</v>
       </c>
@@ -1730,7 +1772,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>46073</v>
       </c>
@@ -1771,8 +1813,176 @@
         <v>88</v>
       </c>
     </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>46074</v>
+      </c>
+      <c r="B22" t="s">
+        <v>99</v>
+      </c>
+      <c r="C22" t="s">
+        <v>159</v>
+      </c>
+      <c r="D22" t="s">
+        <v>100</v>
+      </c>
+      <c r="E22" t="s">
+        <v>112</v>
+      </c>
+      <c r="F22" t="s">
+        <v>118</v>
+      </c>
+      <c r="G22" t="s">
+        <v>90</v>
+      </c>
+      <c r="H22" t="s">
+        <v>160</v>
+      </c>
+      <c r="I22" t="s">
+        <v>120</v>
+      </c>
+      <c r="J22" t="s">
+        <v>119</v>
+      </c>
+      <c r="K22" t="s">
+        <v>117</v>
+      </c>
+      <c r="L22" t="s">
+        <v>161</v>
+      </c>
+      <c r="M22" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>46074</v>
+      </c>
+      <c r="B23" t="s">
+        <v>164</v>
+      </c>
+      <c r="C23" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" t="s">
+        <v>121</v>
+      </c>
+      <c r="E23" t="s">
+        <v>122</v>
+      </c>
+      <c r="F23" t="s">
+        <v>129</v>
+      </c>
+      <c r="G23" t="s">
+        <v>165</v>
+      </c>
+      <c r="H23" t="s">
+        <v>166</v>
+      </c>
+      <c r="I23" t="s">
+        <v>167</v>
+      </c>
+      <c r="J23" t="s">
+        <v>168</v>
+      </c>
+      <c r="K23" t="s">
+        <v>169</v>
+      </c>
+      <c r="L23" t="s">
+        <v>170</v>
+      </c>
+      <c r="M23" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <v>46075</v>
+      </c>
+      <c r="B24" t="s">
+        <v>99</v>
+      </c>
+      <c r="C24" t="s">
+        <v>163</v>
+      </c>
+      <c r="D24" t="s">
+        <v>131</v>
+      </c>
+      <c r="E24" t="s">
+        <v>132</v>
+      </c>
+      <c r="F24" t="s">
+        <v>17</v>
+      </c>
+      <c r="G24" t="s">
+        <v>19</v>
+      </c>
+      <c r="H24" t="s">
+        <v>102</v>
+      </c>
+      <c r="I24" t="s">
+        <v>137</v>
+      </c>
+      <c r="J24" t="s">
+        <v>140</v>
+      </c>
+      <c r="K24" t="s">
+        <v>133</v>
+      </c>
+      <c r="L24" t="s">
+        <v>105</v>
+      </c>
+      <c r="M24" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <v>46075</v>
+      </c>
+      <c r="B25" t="s">
+        <v>164</v>
+      </c>
+      <c r="C25" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25" t="s">
+        <v>144</v>
+      </c>
+      <c r="E25" t="s">
+        <v>145</v>
+      </c>
+      <c r="F25" t="s">
+        <v>143</v>
+      </c>
+      <c r="G25" t="s">
+        <v>88</v>
+      </c>
+      <c r="H25" t="s">
+        <v>151</v>
+      </c>
+      <c r="I25" t="s">
+        <v>146</v>
+      </c>
+      <c r="J25" t="s">
+        <v>171</v>
+      </c>
+      <c r="K25" t="s">
+        <v>147</v>
+      </c>
+      <c r="L25" t="s">
+        <v>150</v>
+      </c>
+      <c r="M25" t="s">
+        <v>172</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M20" xr:uid="{6820EB03-3F7F-49BA-9E92-28FA32BF7E1D}"/>
+  <autoFilter ref="A1:M20" xr:uid="{6820EB03-3F7F-49BA-9E92-28FA32BF7E1D}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M25">
+      <sortCondition ref="A1:A20"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/results.xlsx
+++ b/results.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Desktop/Fantasy Cycling/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DPshonyak\OneDrive - BluCurrent Credit Union\Desktop\Fantasy Cycling\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="6_{791E1E6D-5D1E-411A-AA39-81A4A2AEEE1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0002310A-C130-4D5A-9322-979BD1AC058D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B25D08E-C755-4F16-B35D-7FBCFF41D400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D48BDCD1-ADE3-4EE7-A9DB-3C7F51FF7246}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="172">
   <si>
     <t>Stage 1</t>
   </si>
@@ -531,9 +531,6 @@
   </si>
   <si>
     <t>Stage 7</t>
-  </si>
-  <si>
-    <t>Volta ao Algarve</t>
   </si>
   <si>
     <t>T. T. Teutenberg</t>
@@ -1859,7 +1856,7 @@
         <v>46074</v>
       </c>
       <c r="B23" t="s">
-        <v>164</v>
+        <v>130</v>
       </c>
       <c r="C23" t="s">
         <v>51</v>
@@ -1874,22 +1871,22 @@
         <v>129</v>
       </c>
       <c r="G23" t="s">
+        <v>164</v>
+      </c>
+      <c r="H23" t="s">
         <v>165</v>
       </c>
-      <c r="H23" t="s">
+      <c r="I23" t="s">
         <v>166</v>
       </c>
-      <c r="I23" t="s">
+      <c r="J23" t="s">
         <v>167</v>
       </c>
-      <c r="J23" t="s">
+      <c r="K23" t="s">
         <v>168</v>
       </c>
-      <c r="K23" t="s">
+      <c r="L23" t="s">
         <v>169</v>
-      </c>
-      <c r="L23" t="s">
-        <v>170</v>
       </c>
       <c r="M23" t="s">
         <v>124</v>
@@ -1941,7 +1938,7 @@
         <v>46075</v>
       </c>
       <c r="B25" t="s">
-        <v>164</v>
+        <v>130</v>
       </c>
       <c r="C25" t="s">
         <v>55</v>
@@ -1965,7 +1962,7 @@
         <v>146</v>
       </c>
       <c r="J25" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K25" t="s">
         <v>147</v>
@@ -1974,7 +1971,7 @@
         <v>150</v>
       </c>
       <c r="M25" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>

--- a/results.xlsx
+++ b/results.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DPshonyak\OneDrive - BluCurrent Credit Union\Desktop\Fantasy Cycling\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Desktop/Fantasy Cycling/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B25D08E-C755-4F16-B35D-7FBCFF41D400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>

--- a/results.xlsx
+++ b/results.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Desktop/Fantasy Cycling/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DPshonyak\OneDrive - BluCurrent Credit Union\Desktop\Fantasy Cycling\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B25D08E-C755-4F16-B35D-7FBCFF41D400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C193552-8267-4083-B3AB-168CA7CCEC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D48BDCD1-ADE3-4EE7-A9DB-3C7F51FF7246}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="190">
   <si>
     <t>Stage 1</t>
   </si>
@@ -555,6 +555,60 @@
   </si>
   <si>
     <t>Dylan van Baarle</t>
+  </si>
+  <si>
+    <t>Omloop Het Nieuwsblad</t>
+  </si>
+  <si>
+    <t>One Day</t>
+  </si>
+  <si>
+    <t>Mathieu van der Poel</t>
+  </si>
+  <si>
+    <t>Tim van Dijke</t>
+  </si>
+  <si>
+    <t>Christophe Laporte</t>
+  </si>
+  <si>
+    <t>Aimé De Gendt</t>
+  </si>
+  <si>
+    <t>Anthony Turgis</t>
+  </si>
+  <si>
+    <t>Alexis Renard</t>
+  </si>
+  <si>
+    <t>Faun-Ardèche Classic</t>
+  </si>
+  <si>
+    <t>Jan Christen</t>
+  </si>
+  <si>
+    <t>Lenny Martinez</t>
+  </si>
+  <si>
+    <t>Matteo Jorgenson</t>
+  </si>
+  <si>
+    <t>Mattias Skjelmose</t>
+  </si>
+  <si>
+    <t>Davide Piganzoli</t>
+  </si>
+  <si>
+    <t>Egan Bernal</t>
+  </si>
+  <si>
+    <t>Jefferson Cepeda</t>
+  </si>
+  <si>
+    <t>Igor Arrieta</t>
+  </si>
+  <si>
+    <t>Mattéo Vercher</t>
   </si>
 </sst>
 </file>
@@ -933,7 +987,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6820EB03-3F7F-49BA-9E92-28FA32BF7E1D}">
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
@@ -1974,6 +2028,88 @@
         <v>171</v>
       </c>
     </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <v>46081</v>
+      </c>
+      <c r="B26" t="s">
+        <v>172</v>
+      </c>
+      <c r="C26" t="s">
+        <v>173</v>
+      </c>
+      <c r="D26" t="s">
+        <v>174</v>
+      </c>
+      <c r="E26" t="s">
+        <v>175</v>
+      </c>
+      <c r="F26" t="s">
+        <v>77</v>
+      </c>
+      <c r="G26" t="s">
+        <v>176</v>
+      </c>
+      <c r="H26" t="s">
+        <v>177</v>
+      </c>
+      <c r="I26" t="s">
+        <v>15</v>
+      </c>
+      <c r="J26" t="s">
+        <v>122</v>
+      </c>
+      <c r="K26" t="s">
+        <v>178</v>
+      </c>
+      <c r="L26" t="s">
+        <v>179</v>
+      </c>
+      <c r="M26" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <v>46081</v>
+      </c>
+      <c r="B27" t="s">
+        <v>180</v>
+      </c>
+      <c r="C27" t="s">
+        <v>173</v>
+      </c>
+      <c r="D27" t="s">
+        <v>143</v>
+      </c>
+      <c r="E27" t="s">
+        <v>181</v>
+      </c>
+      <c r="F27" t="s">
+        <v>182</v>
+      </c>
+      <c r="G27" t="s">
+        <v>183</v>
+      </c>
+      <c r="H27" t="s">
+        <v>184</v>
+      </c>
+      <c r="I27" t="s">
+        <v>185</v>
+      </c>
+      <c r="J27" t="s">
+        <v>186</v>
+      </c>
+      <c r="K27" t="s">
+        <v>187</v>
+      </c>
+      <c r="L27" t="s">
+        <v>188</v>
+      </c>
+      <c r="M27" t="s">
+        <v>189</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M20" xr:uid="{6820EB03-3F7F-49BA-9E92-28FA32BF7E1D}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M25">

--- a/results.xlsx
+++ b/results.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DPshonyak\OneDrive - BluCurrent Credit Union\Desktop\Fantasy Cycling\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Desktop/Fantasy Cycling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C193552-8267-4083-B3AB-168CA7CCEC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{8C193552-8267-4083-B3AB-168CA7CCEC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{608A12A9-3E43-46E7-B348-FF0B193BD58B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D48BDCD1-ADE3-4EE7-A9DB-3C7F51FF7246}"/>
   </bookViews>
@@ -557,9 +557,6 @@
     <t>Dylan van Baarle</t>
   </si>
   <si>
-    <t>Omloop Het Nieuwsblad</t>
-  </si>
-  <si>
     <t>One Day</t>
   </si>
   <si>
@@ -609,6 +606,9 @@
   </si>
   <si>
     <t>Mattéo Vercher</t>
+  </si>
+  <si>
+    <t>Omloop Nieuwsblad</t>
   </si>
 </sst>
 </file>
@@ -2033,25 +2033,25 @@
         <v>46081</v>
       </c>
       <c r="B26" t="s">
+        <v>189</v>
+      </c>
+      <c r="C26" t="s">
         <v>172</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>173</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>174</v>
-      </c>
-      <c r="E26" t="s">
-        <v>175</v>
       </c>
       <c r="F26" t="s">
         <v>77</v>
       </c>
       <c r="G26" t="s">
+        <v>175</v>
+      </c>
+      <c r="H26" t="s">
         <v>176</v>
-      </c>
-      <c r="H26" t="s">
-        <v>177</v>
       </c>
       <c r="I26" t="s">
         <v>15</v>
@@ -2060,10 +2060,10 @@
         <v>122</v>
       </c>
       <c r="K26" t="s">
+        <v>177</v>
+      </c>
+      <c r="L26" t="s">
         <v>178</v>
-      </c>
-      <c r="L26" t="s">
-        <v>179</v>
       </c>
       <c r="M26" t="s">
         <v>24</v>
@@ -2074,40 +2074,40 @@
         <v>46081</v>
       </c>
       <c r="B27" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C27" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D27" t="s">
         <v>143</v>
       </c>
       <c r="E27" t="s">
+        <v>180</v>
+      </c>
+      <c r="F27" t="s">
         <v>181</v>
       </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
         <v>182</v>
       </c>
-      <c r="G27" t="s">
+      <c r="H27" t="s">
         <v>183</v>
       </c>
-      <c r="H27" t="s">
+      <c r="I27" t="s">
         <v>184</v>
       </c>
-      <c r="I27" t="s">
+      <c r="J27" t="s">
         <v>185</v>
       </c>
-      <c r="J27" t="s">
+      <c r="K27" t="s">
         <v>186</v>
       </c>
-      <c r="K27" t="s">
+      <c r="L27" t="s">
         <v>187</v>
       </c>
-      <c r="L27" t="s">
+      <c r="M27" t="s">
         <v>188</v>
-      </c>
-      <c r="M27" t="s">
-        <v>189</v>
       </c>
     </row>
   </sheetData>

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Desktop/Fantasy Cycling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{8C193552-8267-4083-B3AB-168CA7CCEC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{608A12A9-3E43-46E7-B348-FF0B193BD58B}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{8C193552-8267-4083-B3AB-168CA7CCEC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD80F52E-A24D-4C98-B5E0-36DC15287A3E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D48BDCD1-ADE3-4EE7-A9DB-3C7F51FF7246}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="203">
   <si>
     <t>Stage 1</t>
   </si>
@@ -609,6 +609,45 @@
   </si>
   <si>
     <t>Omloop Nieuwsblad</t>
+  </si>
+  <si>
+    <t>Kuurne - Brussel - Kuurne</t>
+  </si>
+  <si>
+    <t>Faun Drôme Classic</t>
+  </si>
+  <si>
+    <t>Romain Grégoire</t>
+  </si>
+  <si>
+    <t>Quinten Hermans</t>
+  </si>
+  <si>
+    <t>Paul Lapeira</t>
+  </si>
+  <si>
+    <t>Dorian Godon</t>
+  </si>
+  <si>
+    <t>Christian Scaroni</t>
+  </si>
+  <si>
+    <t>Alex Aranburu</t>
+  </si>
+  <si>
+    <t>Lukas Nerurkar</t>
+  </si>
+  <si>
+    <t>Clément Venturini</t>
+  </si>
+  <si>
+    <t>Matteo Trentin</t>
+  </si>
+  <si>
+    <t>Matevž Govekar</t>
+  </si>
+  <si>
+    <t>Mike Teunissen</t>
   </si>
 </sst>
 </file>
@@ -987,7 +1026,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6820EB03-3F7F-49BA-9E92-28FA32BF7E1D}">
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
@@ -2110,6 +2149,73 @@
         <v>188</v>
       </c>
     </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <v>46082</v>
+      </c>
+      <c r="B28" t="s">
+        <v>191</v>
+      </c>
+      <c r="C28" t="s">
+        <v>172</v>
+      </c>
+      <c r="D28" t="s">
+        <v>192</v>
+      </c>
+      <c r="E28" t="s">
+        <v>182</v>
+      </c>
+      <c r="F28" t="s">
+        <v>181</v>
+      </c>
+      <c r="G28" t="s">
+        <v>193</v>
+      </c>
+      <c r="H28" t="s">
+        <v>194</v>
+      </c>
+      <c r="I28" t="s">
+        <v>195</v>
+      </c>
+      <c r="J28" t="s">
+        <v>196</v>
+      </c>
+      <c r="K28" t="s">
+        <v>197</v>
+      </c>
+      <c r="L28" t="s">
+        <v>198</v>
+      </c>
+      <c r="M28" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <v>46082</v>
+      </c>
+      <c r="B29" t="s">
+        <v>190</v>
+      </c>
+      <c r="C29" t="s">
+        <v>172</v>
+      </c>
+      <c r="D29" t="s">
+        <v>16</v>
+      </c>
+      <c r="E29" t="s">
+        <v>166</v>
+      </c>
+      <c r="F29" t="s">
+        <v>200</v>
+      </c>
+      <c r="G29" t="s">
+        <v>201</v>
+      </c>
+      <c r="H29" t="s">
+        <v>202</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M20" xr:uid="{6820EB03-3F7F-49BA-9E92-28FA32BF7E1D}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M25">

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Desktop/Fantasy Cycling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{8C193552-8267-4083-B3AB-168CA7CCEC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD80F52E-A24D-4C98-B5E0-36DC15287A3E}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{8C193552-8267-4083-B3AB-168CA7CCEC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85C79C70-6693-4D91-848C-B3BB7ACC14BF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D48BDCD1-ADE3-4EE7-A9DB-3C7F51FF7246}"/>
   </bookViews>
@@ -614,9 +614,6 @@
     <t>Kuurne - Brussel - Kuurne</t>
   </si>
   <si>
-    <t>Faun Drôme Classic</t>
-  </si>
-  <si>
     <t>Romain Grégoire</t>
   </si>
   <si>
@@ -648,6 +645,9 @@
   </si>
   <si>
     <t>Mike Teunissen</t>
+  </si>
+  <si>
+    <t>Faun Drome Classic</t>
   </si>
 </sst>
 </file>
@@ -2154,13 +2154,13 @@
         <v>46082</v>
       </c>
       <c r="B28" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="C28" t="s">
         <v>172</v>
       </c>
       <c r="D28" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E28" t="s">
         <v>182</v>
@@ -2169,25 +2169,25 @@
         <v>181</v>
       </c>
       <c r="G28" t="s">
+        <v>192</v>
+      </c>
+      <c r="H28" t="s">
         <v>193</v>
       </c>
-      <c r="H28" t="s">
+      <c r="I28" t="s">
         <v>194</v>
       </c>
-      <c r="I28" t="s">
+      <c r="J28" t="s">
         <v>195</v>
       </c>
-      <c r="J28" t="s">
+      <c r="K28" t="s">
         <v>196</v>
       </c>
-      <c r="K28" t="s">
+      <c r="L28" t="s">
         <v>197</v>
       </c>
-      <c r="L28" t="s">
+      <c r="M28" t="s">
         <v>198</v>
-      </c>
-      <c r="M28" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.3">
@@ -2207,13 +2207,13 @@
         <v>166</v>
       </c>
       <c r="F29" t="s">
+        <v>199</v>
+      </c>
+      <c r="G29" t="s">
         <v>200</v>
       </c>
-      <c r="G29" t="s">
+      <c r="H29" t="s">
         <v>201</v>
-      </c>
-      <c r="H29" t="s">
-        <v>202</v>
       </c>
     </row>
   </sheetData>

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Desktop/Fantasy Cycling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{8C193552-8267-4083-B3AB-168CA7CCEC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85C79C70-6693-4D91-848C-B3BB7ACC14BF}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{8C193552-8267-4083-B3AB-168CA7CCEC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B3B0C8F-0521-4E94-A71C-92741C4B35F6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D48BDCD1-ADE3-4EE7-A9DB-3C7F51FF7246}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="204">
   <si>
     <t>Stage 1</t>
   </si>
@@ -648,6 +648,9 @@
   </si>
   <si>
     <t>Faun Drome Classic</t>
+  </si>
+  <si>
+    <t>Laurenz Rex</t>
   </si>
 </sst>
 </file>
@@ -2215,6 +2218,21 @@
       <c r="H29" t="s">
         <v>201</v>
       </c>
+      <c r="I29" t="s">
+        <v>203</v>
+      </c>
+      <c r="J29" t="s">
+        <v>15</v>
+      </c>
+      <c r="K29" t="s">
+        <v>101</v>
+      </c>
+      <c r="L29" t="s">
+        <v>24</v>
+      </c>
+      <c r="M29" t="s">
+        <v>122</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:M20" xr:uid="{6820EB03-3F7F-49BA-9E92-28FA32BF7E1D}">

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Desktop/Fantasy Cycling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{8C193552-8267-4083-B3AB-168CA7CCEC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B3B0C8F-0521-4E94-A71C-92741C4B35F6}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{8C193552-8267-4083-B3AB-168CA7CCEC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72AE7614-758E-4797-8035-456AEACD6846}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D48BDCD1-ADE3-4EE7-A9DB-3C7F51FF7246}"/>
+    <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{D48BDCD1-ADE3-4EE7-A9DB-3C7F51FF7246}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="220">
   <si>
     <t>Stage 1</t>
   </si>
@@ -651,6 +651,54 @@
   </si>
   <si>
     <t>Laurenz Rex</t>
+  </si>
+  <si>
+    <t>Strade Bianche</t>
+  </si>
+  <si>
+    <t>Tadej Pogačar</t>
+  </si>
+  <si>
+    <t>Gianni Vermeersch</t>
+  </si>
+  <si>
+    <t>Thomas Pidcock</t>
+  </si>
+  <si>
+    <t>Wout van Aert</t>
+  </si>
+  <si>
+    <t>Paris-Nice</t>
+  </si>
+  <si>
+    <t>Vito Braet</t>
+  </si>
+  <si>
+    <t>Orluis Aular</t>
+  </si>
+  <si>
+    <t>Milan Fretin</t>
+  </si>
+  <si>
+    <t>S. Koller Løland</t>
+  </si>
+  <si>
+    <t>Axel Zingle</t>
+  </si>
+  <si>
+    <t>Robert Donaldson</t>
+  </si>
+  <si>
+    <t>Tirreno-Adriatico</t>
+  </si>
+  <si>
+    <t>Max Walscheid</t>
+  </si>
+  <si>
+    <t>Alan Hatherly</t>
+  </si>
+  <si>
+    <t>Primož Roglič</t>
   </si>
 </sst>
 </file>
@@ -1029,23 +1077,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6820EB03-3F7F-49BA-9E92-28FA32BF7E1D}">
-  <dimension ref="A1:M29"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M32"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.5703125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>42</v>
       </c>
@@ -1086,7 +1134,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46042</v>
       </c>
@@ -1127,7 +1175,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>46043</v>
       </c>
@@ -1168,7 +1216,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>46044</v>
       </c>
@@ -1209,7 +1257,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>46045</v>
       </c>
@@ -1250,7 +1298,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>46046</v>
       </c>
@@ -1291,7 +1339,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>46047</v>
       </c>
@@ -1332,7 +1380,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>46054</v>
       </c>
@@ -1373,7 +1421,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>46057</v>
       </c>
@@ -1414,7 +1462,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>46058</v>
       </c>
@@ -1455,7 +1503,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>46059</v>
       </c>
@@ -1496,7 +1544,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>46060</v>
       </c>
@@ -1537,7 +1585,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>46061</v>
       </c>
@@ -1578,7 +1626,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>46069</v>
       </c>
@@ -1619,7 +1667,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>46070</v>
       </c>
@@ -1660,7 +1708,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>46071</v>
       </c>
@@ -1701,7 +1749,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>46071</v>
       </c>
@@ -1742,7 +1790,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>46072</v>
       </c>
@@ -1783,7 +1831,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>46072</v>
       </c>
@@ -1824,7 +1872,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>46073</v>
       </c>
@@ -1865,7 +1913,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>46073</v>
       </c>
@@ -1906,7 +1954,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>46074</v>
       </c>
@@ -1947,7 +1995,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>46074</v>
       </c>
@@ -1988,7 +2036,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>46075</v>
       </c>
@@ -2029,7 +2077,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>46075</v>
       </c>
@@ -2070,7 +2118,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>46081</v>
       </c>
@@ -2111,7 +2159,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>46081</v>
       </c>
@@ -2152,7 +2200,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>46082</v>
       </c>
@@ -2193,7 +2241,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>46082</v>
       </c>
@@ -2232,6 +2280,129 @@
       </c>
       <c r="M29" t="s">
         <v>122</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>46088</v>
+      </c>
+      <c r="B30" t="s">
+        <v>204</v>
+      </c>
+      <c r="C30" t="s">
+        <v>172</v>
+      </c>
+      <c r="D30" t="s">
+        <v>205</v>
+      </c>
+      <c r="E30" t="s">
+        <v>143</v>
+      </c>
+      <c r="F30" t="s">
+        <v>116</v>
+      </c>
+      <c r="G30" t="s">
+        <v>191</v>
+      </c>
+      <c r="H30" t="s">
+        <v>206</v>
+      </c>
+      <c r="I30" t="s">
+        <v>180</v>
+      </c>
+      <c r="J30" t="s">
+        <v>207</v>
+      </c>
+      <c r="K30" t="s">
+        <v>182</v>
+      </c>
+      <c r="L30" t="s">
+        <v>28</v>
+      </c>
+      <c r="M30" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>46089</v>
+      </c>
+      <c r="B31" t="s">
+        <v>209</v>
+      </c>
+      <c r="C31" t="s">
+        <v>0</v>
+      </c>
+      <c r="D31" t="s">
+        <v>24</v>
+      </c>
+      <c r="E31" t="s">
+        <v>210</v>
+      </c>
+      <c r="F31" t="s">
+        <v>211</v>
+      </c>
+      <c r="G31" t="s">
+        <v>212</v>
+      </c>
+      <c r="H31" t="s">
+        <v>64</v>
+      </c>
+      <c r="I31" t="s">
+        <v>41</v>
+      </c>
+      <c r="J31" t="s">
+        <v>201</v>
+      </c>
+      <c r="K31" t="s">
+        <v>213</v>
+      </c>
+      <c r="L31" t="s">
+        <v>214</v>
+      </c>
+      <c r="M31" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>46090</v>
+      </c>
+      <c r="B32" t="s">
+        <v>216</v>
+      </c>
+      <c r="C32" t="s">
+        <v>0</v>
+      </c>
+      <c r="D32" t="s">
+        <v>153</v>
+      </c>
+      <c r="E32" t="s">
+        <v>155</v>
+      </c>
+      <c r="F32" t="s">
+        <v>217</v>
+      </c>
+      <c r="G32" t="s">
+        <v>78</v>
+      </c>
+      <c r="H32" t="s">
+        <v>131</v>
+      </c>
+      <c r="I32" t="s">
+        <v>218</v>
+      </c>
+      <c r="J32" t="s">
+        <v>219</v>
+      </c>
+      <c r="K32" t="s">
+        <v>110</v>
+      </c>
+      <c r="L32" t="s">
+        <v>90</v>
+      </c>
+      <c r="M32" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Desktop/Fantasy Cycling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{8C193552-8267-4083-B3AB-168CA7CCEC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72AE7614-758E-4797-8035-456AEACD6846}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{8C193552-8267-4083-B3AB-168CA7CCEC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68DF2109-21AD-4594-A775-0443BC00C1EA}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{D48BDCD1-ADE3-4EE7-A9DB-3C7F51FF7246}"/>
   </bookViews>
@@ -662,9 +662,6 @@
     <t>Gianni Vermeersch</t>
   </si>
   <si>
-    <t>Thomas Pidcock</t>
-  </si>
-  <si>
     <t>Wout van Aert</t>
   </si>
   <si>
@@ -699,6 +696,9 @@
   </si>
   <si>
     <t>Primož Roglič</t>
+  </si>
+  <si>
+    <t>Tom Pidcock</t>
   </si>
 </sst>
 </file>
@@ -2311,7 +2311,7 @@
         <v>180</v>
       </c>
       <c r="J30" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="K30" t="s">
         <v>182</v>
@@ -2320,7 +2320,7 @@
         <v>28</v>
       </c>
       <c r="M30" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
@@ -2328,7 +2328,7 @@
         <v>46089</v>
       </c>
       <c r="B31" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C31" t="s">
         <v>0</v>
@@ -2337,13 +2337,13 @@
         <v>24</v>
       </c>
       <c r="E31" t="s">
+        <v>209</v>
+      </c>
+      <c r="F31" t="s">
         <v>210</v>
       </c>
-      <c r="F31" t="s">
+      <c r="G31" t="s">
         <v>211</v>
-      </c>
-      <c r="G31" t="s">
-        <v>212</v>
       </c>
       <c r="H31" t="s">
         <v>64</v>
@@ -2355,13 +2355,13 @@
         <v>201</v>
       </c>
       <c r="K31" t="s">
+        <v>212</v>
+      </c>
+      <c r="L31" t="s">
         <v>213</v>
       </c>
-      <c r="L31" t="s">
+      <c r="M31" t="s">
         <v>214</v>
-      </c>
-      <c r="M31" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
@@ -2369,7 +2369,7 @@
         <v>46090</v>
       </c>
       <c r="B32" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C32" t="s">
         <v>0</v>
@@ -2381,7 +2381,7 @@
         <v>155</v>
       </c>
       <c r="F32" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G32" t="s">
         <v>78</v>
@@ -2390,10 +2390,10 @@
         <v>131</v>
       </c>
       <c r="I32" t="s">
+        <v>217</v>
+      </c>
+      <c r="J32" t="s">
         <v>218</v>
-      </c>
-      <c r="J32" t="s">
-        <v>219</v>
       </c>
       <c r="K32" t="s">
         <v>110</v>

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Desktop/Fantasy Cycling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{8C193552-8267-4083-B3AB-168CA7CCEC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68DF2109-21AD-4594-A775-0443BC00C1EA}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="13_ncr:1_{8C193552-8267-4083-B3AB-168CA7CCEC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{364BE9CD-F42F-4569-A385-9B8ABE1AC8EB}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{D48BDCD1-ADE3-4EE7-A9DB-3C7F51FF7246}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="224">
   <si>
     <t>Stage 1</t>
   </si>
@@ -699,6 +699,18 @@
   </si>
   <si>
     <t>Tom Pidcock</t>
+  </si>
+  <si>
+    <t>T. Halland Johannessen</t>
+  </si>
+  <si>
+    <t>Andrea Vendrame</t>
+  </si>
+  <si>
+    <t>Giulio Ciccone</t>
+  </si>
+  <si>
+    <t>Clément Champoussin</t>
   </si>
 </sst>
 </file>
@@ -1077,7 +1089,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6820EB03-3F7F-49BA-9E92-28FA32BF7E1D}">
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -2405,6 +2417,47 @@
         <v>116</v>
       </c>
     </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B33" t="s">
+        <v>215</v>
+      </c>
+      <c r="C33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D33" t="s">
+        <v>173</v>
+      </c>
+      <c r="E33" t="s">
+        <v>116</v>
+      </c>
+      <c r="F33" t="s">
+        <v>89</v>
+      </c>
+      <c r="G33" t="s">
+        <v>220</v>
+      </c>
+      <c r="H33" t="s">
+        <v>221</v>
+      </c>
+      <c r="I33" t="s">
+        <v>148</v>
+      </c>
+      <c r="J33" t="s">
+        <v>222</v>
+      </c>
+      <c r="K33" t="s">
+        <v>28</v>
+      </c>
+      <c r="L33" t="s">
+        <v>223</v>
+      </c>
+      <c r="M33" t="s">
+        <v>193</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M20" xr:uid="{6820EB03-3F7F-49BA-9E92-28FA32BF7E1D}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M25">

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Desktop/Fantasy Cycling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="13_ncr:1_{8C193552-8267-4083-B3AB-168CA7CCEC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{364BE9CD-F42F-4569-A385-9B8ABE1AC8EB}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{8C193552-8267-4083-B3AB-168CA7CCEC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4DB7A173-D0C3-4398-BE5E-C4596919C3D2}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{D48BDCD1-ADE3-4EE7-A9DB-3C7F51FF7246}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="223">
   <si>
     <t>Stage 1</t>
   </si>
@@ -699,9 +699,6 @@
   </si>
   <si>
     <t>Tom Pidcock</t>
-  </si>
-  <si>
-    <t>T. Halland Johannessen</t>
   </si>
   <si>
     <t>Andrea Vendrame</t>
@@ -2437,22 +2434,22 @@
         <v>89</v>
       </c>
       <c r="G33" t="s">
+        <v>107</v>
+      </c>
+      <c r="H33" t="s">
         <v>220</v>
-      </c>
-      <c r="H33" t="s">
-        <v>221</v>
       </c>
       <c r="I33" t="s">
         <v>148</v>
       </c>
       <c r="J33" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="K33" t="s">
         <v>28</v>
       </c>
       <c r="L33" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="M33" t="s">
         <v>193</v>

--- a/results.xlsx
+++ b/results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Desktop/Fantasy Cycling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{8C193552-8267-4083-B3AB-168CA7CCEC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4DB7A173-D0C3-4398-BE5E-C4596919C3D2}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{8C193552-8267-4083-B3AB-168CA7CCEC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A287C799-34C9-41A3-8A86-5F2E81810F9D}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{D48BDCD1-ADE3-4EE7-A9DB-3C7F51FF7246}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="229">
   <si>
     <t>Stage 1</t>
   </si>
@@ -708,6 +708,24 @@
   </si>
   <si>
     <t>Clément Champoussin</t>
+  </si>
+  <si>
+    <t>Jonas Vingegaard</t>
+  </si>
+  <si>
+    <t>Daniel Felipe Martínez</t>
+  </si>
+  <si>
+    <t>Mick van Dijke</t>
+  </si>
+  <si>
+    <t>Georg Steinhauser</t>
+  </si>
+  <si>
+    <t>Marc Soler</t>
+  </si>
+  <si>
+    <t>Iván García Cortina</t>
   </si>
 </sst>
 </file>
@@ -1086,17 +1104,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6820EB03-3F7F-49BA-9E92-28FA32BF7E1D}">
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="33.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="6" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="27" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="19.140625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="23.5703125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="27" bestFit="1" customWidth="1"/>
@@ -2453,6 +2471,88 @@
       </c>
       <c r="M33" t="s">
         <v>193</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B34" t="s">
+        <v>215</v>
+      </c>
+      <c r="C34" t="s">
+        <v>43</v>
+      </c>
+      <c r="D34" t="s">
+        <v>15</v>
+      </c>
+      <c r="E34" t="s">
+        <v>125</v>
+      </c>
+      <c r="F34" t="s">
+        <v>124</v>
+      </c>
+      <c r="G34" t="s">
+        <v>121</v>
+      </c>
+      <c r="H34" t="s">
+        <v>228</v>
+      </c>
+      <c r="I34" t="s">
+        <v>17</v>
+      </c>
+      <c r="J34" t="s">
+        <v>131</v>
+      </c>
+      <c r="K34" t="s">
+        <v>129</v>
+      </c>
+      <c r="L34" t="s">
+        <v>137</v>
+      </c>
+      <c r="M34" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B35" t="s">
+        <v>208</v>
+      </c>
+      <c r="C35" t="s">
+        <v>51</v>
+      </c>
+      <c r="D35" t="s">
+        <v>223</v>
+      </c>
+      <c r="E35" t="s">
+        <v>224</v>
+      </c>
+      <c r="F35" t="s">
+        <v>174</v>
+      </c>
+      <c r="G35" t="s">
+        <v>225</v>
+      </c>
+      <c r="H35" t="s">
+        <v>226</v>
+      </c>
+      <c r="I35" t="s">
+        <v>150</v>
+      </c>
+      <c r="J35" t="s">
+        <v>181</v>
+      </c>
+      <c r="K35" t="s">
+        <v>161</v>
+      </c>
+      <c r="L35" t="s">
+        <v>41</v>
+      </c>
+      <c r="M35" t="s">
+        <v>227</v>
       </c>
     </row>
   </sheetData>

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Desktop/Fantasy Cycling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{8C193552-8267-4083-B3AB-168CA7CCEC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A287C799-34C9-41A3-8A86-5F2E81810F9D}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{8C193552-8267-4083-B3AB-168CA7CCEC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ADDACEA2-6EFD-47DF-86AB-95DAF7A22018}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{D48BDCD1-ADE3-4EE7-A9DB-3C7F51FF7246}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="230">
   <si>
     <t>Stage 1</t>
   </si>
@@ -726,6 +726,9 @@
   </si>
   <si>
     <t>Iván García Cortina</t>
+  </si>
+  <si>
+    <t>Ben Healy</t>
   </si>
 </sst>
 </file>
@@ -1104,7 +1107,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6820EB03-3F7F-49BA-9E92-28FA32BF7E1D}">
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -2555,6 +2558,47 @@
         <v>227</v>
       </c>
     </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B36" t="s">
+        <v>215</v>
+      </c>
+      <c r="C36" t="s">
+        <v>51</v>
+      </c>
+      <c r="D36" t="s">
+        <v>173</v>
+      </c>
+      <c r="E36" t="s">
+        <v>89</v>
+      </c>
+      <c r="F36" t="s">
+        <v>107</v>
+      </c>
+      <c r="G36" t="s">
+        <v>222</v>
+      </c>
+      <c r="H36" t="s">
+        <v>207</v>
+      </c>
+      <c r="I36" t="s">
+        <v>229</v>
+      </c>
+      <c r="J36" t="s">
+        <v>220</v>
+      </c>
+      <c r="K36" t="s">
+        <v>148</v>
+      </c>
+      <c r="L36" t="s">
+        <v>153</v>
+      </c>
+      <c r="M36" t="s">
+        <v>116</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M20" xr:uid="{6820EB03-3F7F-49BA-9E92-28FA32BF7E1D}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M25">

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Desktop/Fantasy Cycling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{8C193552-8267-4083-B3AB-168CA7CCEC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ADDACEA2-6EFD-47DF-86AB-95DAF7A22018}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="13_ncr:1_{8C193552-8267-4083-B3AB-168CA7CCEC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{796CAA1C-AA1F-41BC-AA09-B148206394F3}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{D48BDCD1-ADE3-4EE7-A9DB-3C7F51FF7246}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="233">
   <si>
     <t>Stage 1</t>
   </si>
@@ -729,6 +729,15 @@
   </si>
   <si>
     <t>Ben Healy</t>
+  </si>
+  <si>
+    <t>Valentin Paret-Peintre</t>
+  </si>
+  <si>
+    <t>Ion Izagirre</t>
+  </si>
+  <si>
+    <t>Mathys Rondel</t>
   </si>
 </sst>
 </file>
@@ -1107,7 +1116,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6820EB03-3F7F-49BA-9E92-28FA32BF7E1D}">
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -2599,6 +2608,47 @@
         <v>116</v>
       </c>
     </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B37" t="s">
+        <v>208</v>
+      </c>
+      <c r="C37" t="s">
+        <v>55</v>
+      </c>
+      <c r="D37" t="s">
+        <v>223</v>
+      </c>
+      <c r="E37" t="s">
+        <v>230</v>
+      </c>
+      <c r="F37" t="s">
+        <v>117</v>
+      </c>
+      <c r="G37" t="s">
+        <v>181</v>
+      </c>
+      <c r="H37" t="s">
+        <v>231</v>
+      </c>
+      <c r="I37" t="s">
+        <v>224</v>
+      </c>
+      <c r="J37" t="s">
+        <v>150</v>
+      </c>
+      <c r="K37" t="s">
+        <v>226</v>
+      </c>
+      <c r="L37" t="s">
+        <v>232</v>
+      </c>
+      <c r="M37" t="s">
+        <v>227</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M20" xr:uid="{6820EB03-3F7F-49BA-9E92-28FA32BF7E1D}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M25">

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Desktop/Fantasy Cycling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40" documentId="13_ncr:1_{8C193552-8267-4083-B3AB-168CA7CCEC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{796CAA1C-AA1F-41BC-AA09-B148206394F3}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="13_ncr:1_{8C193552-8267-4083-B3AB-168CA7CCEC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E33317CA-EAD1-4E6E-822F-20BD4FE9728E}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{D48BDCD1-ADE3-4EE7-A9DB-3C7F51FF7246}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="235">
   <si>
     <t>Stage 1</t>
   </si>
@@ -738,6 +738,12 @@
   </si>
   <si>
     <t>Mathys Rondel</t>
+  </si>
+  <si>
+    <t>Michael Valgren</t>
+  </si>
+  <si>
+    <t>Santiago Buitrago</t>
   </si>
 </sst>
 </file>
@@ -1116,7 +1122,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6820EB03-3F7F-49BA-9E92-28FA32BF7E1D}">
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -2649,6 +2655,47 @@
         <v>227</v>
       </c>
     </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B38" t="s">
+        <v>215</v>
+      </c>
+      <c r="C38" t="s">
+        <v>55</v>
+      </c>
+      <c r="D38" t="s">
+        <v>233</v>
+      </c>
+      <c r="E38" t="s">
+        <v>116</v>
+      </c>
+      <c r="F38" t="s">
+        <v>182</v>
+      </c>
+      <c r="G38" t="s">
+        <v>107</v>
+      </c>
+      <c r="H38" t="s">
+        <v>221</v>
+      </c>
+      <c r="I38" t="s">
+        <v>89</v>
+      </c>
+      <c r="J38" t="s">
+        <v>218</v>
+      </c>
+      <c r="K38" t="s">
+        <v>148</v>
+      </c>
+      <c r="L38" t="s">
+        <v>162</v>
+      </c>
+      <c r="M38" t="s">
+        <v>234</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M20" xr:uid="{6820EB03-3F7F-49BA-9E92-28FA32BF7E1D}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M25">

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Desktop/Fantasy Cycling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="13_ncr:1_{8C193552-8267-4083-B3AB-168CA7CCEC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E33317CA-EAD1-4E6E-822F-20BD4FE9728E}"/>
+  <xr:revisionPtr revIDLastSave="44" documentId="13_ncr:1_{8C193552-8267-4083-B3AB-168CA7CCEC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9CB66D1-0CE6-4FF0-B02C-088C23035755}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{D48BDCD1-ADE3-4EE7-A9DB-3C7F51FF7246}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D48BDCD1-ADE3-4EE7-A9DB-3C7F51FF7246}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="238">
   <si>
     <t>Stage 1</t>
   </si>
@@ -744,6 +744,15 @@
   </si>
   <si>
     <t>Santiago Buitrago</t>
+  </si>
+  <si>
+    <t>Lewis Askey</t>
+  </si>
+  <si>
+    <t>Bryan Coquard</t>
+  </si>
+  <si>
+    <t>Alex Baudin</t>
   </si>
 </sst>
 </file>
@@ -1122,23 +1131,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6820EB03-3F7F-49BA-9E92-28FA32BF7E1D}">
-  <dimension ref="A1:M38"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M39"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="20.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="27" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="27" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.5546875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>42</v>
       </c>
@@ -1179,7 +1188,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>46042</v>
       </c>
@@ -1220,7 +1229,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>46043</v>
       </c>
@@ -1261,7 +1270,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>46044</v>
       </c>
@@ -1302,7 +1311,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>46045</v>
       </c>
@@ -1343,7 +1352,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>46046</v>
       </c>
@@ -1384,7 +1393,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>46047</v>
       </c>
@@ -1425,7 +1434,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>46054</v>
       </c>
@@ -1466,7 +1475,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>46057</v>
       </c>
@@ -1507,7 +1516,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>46058</v>
       </c>
@@ -1548,7 +1557,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>46059</v>
       </c>
@@ -1589,7 +1598,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>46060</v>
       </c>
@@ -1630,7 +1639,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>46061</v>
       </c>
@@ -1671,7 +1680,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>46069</v>
       </c>
@@ -1712,7 +1721,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>46070</v>
       </c>
@@ -1753,7 +1762,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>46071</v>
       </c>
@@ -1794,7 +1803,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>46071</v>
       </c>
@@ -1835,7 +1844,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>46072</v>
       </c>
@@ -1876,7 +1885,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>46072</v>
       </c>
@@ -1917,7 +1926,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>46073</v>
       </c>
@@ -1958,7 +1967,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>46073</v>
       </c>
@@ -1999,7 +2008,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>46074</v>
       </c>
@@ -2040,7 +2049,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>46074</v>
       </c>
@@ -2081,7 +2090,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>46075</v>
       </c>
@@ -2122,7 +2131,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>46075</v>
       </c>
@@ -2163,7 +2172,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>46081</v>
       </c>
@@ -2204,7 +2213,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>46081</v>
       </c>
@@ -2245,7 +2254,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>46082</v>
       </c>
@@ -2286,7 +2295,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>46082</v>
       </c>
@@ -2327,7 +2336,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>46088</v>
       </c>
@@ -2368,7 +2377,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>46089</v>
       </c>
@@ -2409,7 +2418,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>46090</v>
       </c>
@@ -2450,7 +2459,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>46091</v>
       </c>
@@ -2491,7 +2500,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>46092</v>
       </c>
@@ -2532,7 +2541,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>46092</v>
       </c>
@@ -2573,7 +2582,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>46093</v>
       </c>
@@ -2614,7 +2623,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>46093</v>
       </c>
@@ -2655,7 +2664,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>46094</v>
       </c>
@@ -2694,6 +2703,47 @@
       </c>
       <c r="M38" t="s">
         <v>234</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B39" t="s">
+        <v>208</v>
+      </c>
+      <c r="C39" t="s">
+        <v>159</v>
+      </c>
+      <c r="D39" t="s">
+        <v>117</v>
+      </c>
+      <c r="E39" t="s">
+        <v>194</v>
+      </c>
+      <c r="F39" t="s">
+        <v>235</v>
+      </c>
+      <c r="G39" t="s">
+        <v>236</v>
+      </c>
+      <c r="H39" t="s">
+        <v>199</v>
+      </c>
+      <c r="I39" t="s">
+        <v>37</v>
+      </c>
+      <c r="J39" t="s">
+        <v>150</v>
+      </c>
+      <c r="K39" t="s">
+        <v>230</v>
+      </c>
+      <c r="L39" t="s">
+        <v>68</v>
+      </c>
+      <c r="M39" t="s">
+        <v>237</v>
       </c>
     </row>
   </sheetData>

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Desktop/Fantasy Cycling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="44" documentId="13_ncr:1_{8C193552-8267-4083-B3AB-168CA7CCEC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9CB66D1-0CE6-4FF0-B02C-088C23035755}"/>
+  <xr:revisionPtr revIDLastSave="54" documentId="13_ncr:1_{8C193552-8267-4083-B3AB-168CA7CCEC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BCF866F3-633D-4351-911C-7771EA164932}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D48BDCD1-ADE3-4EE7-A9DB-3C7F51FF7246}"/>
+    <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{D48BDCD1-ADE3-4EE7-A9DB-3C7F51FF7246}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="237">
   <si>
     <t>Stage 1</t>
   </si>
@@ -339,9 +339,6 @@
   </si>
   <si>
     <t>UAE Tour</t>
-  </si>
-  <si>
-    <t>Isaac Del Toro</t>
   </si>
   <si>
     <t>Cees Bol</t>
@@ -1132,22 +1129,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6820EB03-3F7F-49BA-9E92-28FA32BF7E1D}">
   <dimension ref="A1:M39"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="20.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="27" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="27" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.5703125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>42</v>
       </c>
@@ -1188,7 +1185,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46042</v>
       </c>
@@ -1229,7 +1226,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>46043</v>
       </c>
@@ -1270,7 +1267,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>46044</v>
       </c>
@@ -1311,7 +1308,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>46045</v>
       </c>
@@ -1352,7 +1349,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>46046</v>
       </c>
@@ -1393,7 +1390,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>46047</v>
       </c>
@@ -1434,7 +1431,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>46054</v>
       </c>
@@ -1475,7 +1472,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>46057</v>
       </c>
@@ -1516,7 +1513,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>46058</v>
       </c>
@@ -1557,7 +1554,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>46059</v>
       </c>
@@ -1598,7 +1595,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>46060</v>
       </c>
@@ -1639,7 +1636,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>46061</v>
       </c>
@@ -1680,7 +1677,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>46069</v>
       </c>
@@ -1691,37 +1688,37 @@
         <v>0</v>
       </c>
       <c r="D14" t="s">
+        <v>115</v>
+      </c>
+      <c r="E14" t="s">
         <v>100</v>
-      </c>
-      <c r="E14" t="s">
-        <v>101</v>
       </c>
       <c r="F14" t="s">
         <v>90</v>
       </c>
       <c r="G14" t="s">
+        <v>101</v>
+      </c>
+      <c r="H14" t="s">
         <v>102</v>
       </c>
-      <c r="H14" t="s">
+      <c r="I14" t="s">
         <v>103</v>
       </c>
-      <c r="I14" t="s">
+      <c r="J14" t="s">
         <v>104</v>
       </c>
-      <c r="J14" t="s">
+      <c r="K14" t="s">
         <v>105</v>
-      </c>
-      <c r="K14" t="s">
-        <v>106</v>
       </c>
       <c r="L14" t="s">
         <v>19</v>
       </c>
       <c r="M14" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>46070</v>
       </c>
@@ -1735,34 +1732,34 @@
         <v>74</v>
       </c>
       <c r="E15" t="s">
+        <v>107</v>
+      </c>
+      <c r="F15" t="s">
         <v>108</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>109</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>110</v>
       </c>
-      <c r="H15" t="s">
+      <c r="I15" t="s">
         <v>111</v>
       </c>
-      <c r="I15" t="s">
+      <c r="J15" t="s">
         <v>112</v>
-      </c>
-      <c r="J15" t="s">
-        <v>113</v>
       </c>
       <c r="K15" t="s">
         <v>77</v>
       </c>
       <c r="L15" t="s">
+        <v>113</v>
+      </c>
+      <c r="M15" t="s">
         <v>114</v>
       </c>
-      <c r="M15" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>46071</v>
       </c>
@@ -1776,75 +1773,75 @@
         <v>90</v>
       </c>
       <c r="E16" t="s">
+        <v>115</v>
+      </c>
+      <c r="F16" t="s">
+        <v>105</v>
+      </c>
+      <c r="G16" t="s">
         <v>116</v>
       </c>
-      <c r="F16" t="s">
+      <c r="H16" t="s">
+        <v>117</v>
+      </c>
+      <c r="I16" t="s">
         <v>106</v>
       </c>
-      <c r="G16" t="s">
-        <v>117</v>
-      </c>
-      <c r="H16" t="s">
+      <c r="J16" t="s">
         <v>118</v>
       </c>
-      <c r="I16" t="s">
-        <v>107</v>
-      </c>
-      <c r="J16" t="s">
+      <c r="K16" t="s">
         <v>119</v>
       </c>
-      <c r="K16" t="s">
-        <v>120</v>
-      </c>
       <c r="L16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M16" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>46071</v>
       </c>
       <c r="B17" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C17" t="s">
         <v>0</v>
       </c>
       <c r="D17" t="s">
+        <v>120</v>
+      </c>
+      <c r="E17" t="s">
         <v>121</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>122</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>123</v>
       </c>
-      <c r="G17" t="s">
+      <c r="H17" t="s">
         <v>124</v>
       </c>
-      <c r="H17" t="s">
+      <c r="I17" t="s">
         <v>125</v>
       </c>
-      <c r="I17" t="s">
+      <c r="J17" t="s">
         <v>126</v>
       </c>
-      <c r="J17" t="s">
+      <c r="K17" t="s">
         <v>127</v>
       </c>
-      <c r="K17" t="s">
+      <c r="L17" t="s">
         <v>128</v>
       </c>
-      <c r="L17" t="s">
-        <v>129</v>
-      </c>
       <c r="M17" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>46072</v>
       </c>
@@ -1855,78 +1852,78 @@
         <v>51</v>
       </c>
       <c r="D18" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E18" t="s">
         <v>19</v>
       </c>
       <c r="F18" t="s">
+        <v>138</v>
+      </c>
+      <c r="G18" t="s">
         <v>139</v>
       </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
         <v>140</v>
       </c>
-      <c r="H18" t="s">
-        <v>141</v>
-      </c>
       <c r="I18" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J18" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K18" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L18" t="s">
         <v>17</v>
       </c>
       <c r="M18" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>46072</v>
       </c>
       <c r="B19" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C19" t="s">
         <v>1</v>
       </c>
       <c r="D19" t="s">
+        <v>142</v>
+      </c>
+      <c r="E19" t="s">
         <v>143</v>
-      </c>
-      <c r="E19" t="s">
-        <v>144</v>
       </c>
       <c r="F19" t="s">
         <v>88</v>
       </c>
       <c r="G19" t="s">
+        <v>144</v>
+      </c>
+      <c r="H19" t="s">
         <v>145</v>
       </c>
-      <c r="H19" t="s">
+      <c r="I19" t="s">
         <v>146</v>
       </c>
-      <c r="I19" t="s">
+      <c r="J19" t="s">
         <v>147</v>
       </c>
-      <c r="J19" t="s">
+      <c r="K19" t="s">
         <v>148</v>
       </c>
-      <c r="K19" t="s">
+      <c r="L19" t="s">
         <v>149</v>
       </c>
-      <c r="L19" t="s">
+      <c r="M19" t="s">
         <v>150</v>
       </c>
-      <c r="M19" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>46073</v>
       </c>
@@ -1937,78 +1934,78 @@
         <v>55</v>
       </c>
       <c r="D20" t="s">
+        <v>130</v>
+      </c>
+      <c r="E20" t="s">
         <v>131</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
+        <v>101</v>
+      </c>
+      <c r="G20" t="s">
         <v>132</v>
       </c>
-      <c r="F20" t="s">
-        <v>102</v>
-      </c>
-      <c r="G20" t="s">
+      <c r="H20" t="s">
         <v>133</v>
-      </c>
-      <c r="H20" t="s">
-        <v>134</v>
       </c>
       <c r="I20" t="s">
         <v>19</v>
       </c>
       <c r="J20" t="s">
+        <v>134</v>
+      </c>
+      <c r="K20" t="s">
         <v>135</v>
       </c>
-      <c r="K20" t="s">
+      <c r="L20" t="s">
         <v>136</v>
       </c>
-      <c r="L20" t="s">
+      <c r="M20" t="s">
         <v>137</v>
       </c>
-      <c r="M20" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>46073</v>
       </c>
       <c r="B21" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C21" t="s">
         <v>43</v>
       </c>
       <c r="D21" t="s">
+        <v>152</v>
+      </c>
+      <c r="E21" t="s">
+        <v>143</v>
+      </c>
+      <c r="F21" t="s">
         <v>153</v>
       </c>
-      <c r="E21" t="s">
-        <v>144</v>
-      </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
+        <v>142</v>
+      </c>
+      <c r="H21" t="s">
         <v>154</v>
       </c>
-      <c r="G21" t="s">
-        <v>143</v>
-      </c>
-      <c r="H21" t="s">
+      <c r="I21" t="s">
+        <v>149</v>
+      </c>
+      <c r="J21" t="s">
         <v>155</v>
       </c>
-      <c r="I21" t="s">
-        <v>150</v>
-      </c>
-      <c r="J21" t="s">
+      <c r="K21" t="s">
         <v>156</v>
       </c>
-      <c r="K21" t="s">
+      <c r="L21" t="s">
         <v>157</v>
-      </c>
-      <c r="L21" t="s">
-        <v>158</v>
       </c>
       <c r="M21" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>46074</v>
       </c>
@@ -2016,81 +2013,81 @@
         <v>99</v>
       </c>
       <c r="C22" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D22" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="E22" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G22" t="s">
         <v>90</v>
       </c>
       <c r="H22" t="s">
+        <v>159</v>
+      </c>
+      <c r="I22" t="s">
+        <v>119</v>
+      </c>
+      <c r="J22" t="s">
+        <v>118</v>
+      </c>
+      <c r="K22" t="s">
+        <v>116</v>
+      </c>
+      <c r="L22" t="s">
         <v>160</v>
       </c>
-      <c r="I22" t="s">
-        <v>120</v>
-      </c>
-      <c r="J22" t="s">
-        <v>119</v>
-      </c>
-      <c r="K22" t="s">
-        <v>117</v>
-      </c>
-      <c r="L22" t="s">
+      <c r="M22" t="s">
         <v>161</v>
       </c>
-      <c r="M22" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>46074</v>
       </c>
       <c r="B23" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C23" t="s">
         <v>51</v>
       </c>
       <c r="D23" t="s">
+        <v>120</v>
+      </c>
+      <c r="E23" t="s">
         <v>121</v>
       </c>
-      <c r="E23" t="s">
-        <v>122</v>
-      </c>
       <c r="F23" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G23" t="s">
+        <v>163</v>
+      </c>
+      <c r="H23" t="s">
         <v>164</v>
       </c>
-      <c r="H23" t="s">
+      <c r="I23" t="s">
         <v>165</v>
       </c>
-      <c r="I23" t="s">
+      <c r="J23" t="s">
         <v>166</v>
       </c>
-      <c r="J23" t="s">
+      <c r="K23" t="s">
         <v>167</v>
       </c>
-      <c r="K23" t="s">
+      <c r="L23" t="s">
         <v>168</v>
       </c>
-      <c r="L23" t="s">
-        <v>169</v>
-      </c>
       <c r="M23" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>46075</v>
       </c>
@@ -2098,13 +2095,13 @@
         <v>99</v>
       </c>
       <c r="C24" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D24" t="s">
+        <v>130</v>
+      </c>
+      <c r="E24" t="s">
         <v>131</v>
-      </c>
-      <c r="E24" t="s">
-        <v>132</v>
       </c>
       <c r="F24" t="s">
         <v>17</v>
@@ -2113,276 +2110,276 @@
         <v>19</v>
       </c>
       <c r="H24" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I24" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J24" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K24" t="s">
+        <v>132</v>
+      </c>
+      <c r="L24" t="s">
+        <v>104</v>
+      </c>
+      <c r="M24" t="s">
         <v>133</v>
       </c>
-      <c r="L24" t="s">
-        <v>105</v>
-      </c>
-      <c r="M24" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>46075</v>
       </c>
       <c r="B25" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C25" t="s">
         <v>55</v>
       </c>
       <c r="D25" t="s">
+        <v>143</v>
+      </c>
+      <c r="E25" t="s">
         <v>144</v>
       </c>
-      <c r="E25" t="s">
-        <v>145</v>
-      </c>
       <c r="F25" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G25" t="s">
         <v>88</v>
       </c>
       <c r="H25" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I25" t="s">
+        <v>145</v>
+      </c>
+      <c r="J25" t="s">
+        <v>169</v>
+      </c>
+      <c r="K25" t="s">
         <v>146</v>
       </c>
-      <c r="J25" t="s">
+      <c r="L25" t="s">
+        <v>149</v>
+      </c>
+      <c r="M25" t="s">
         <v>170</v>
       </c>
-      <c r="K25" t="s">
-        <v>147</v>
-      </c>
-      <c r="L25" t="s">
-        <v>150</v>
-      </c>
-      <c r="M25" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>46081</v>
       </c>
       <c r="B26" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C26" t="s">
+        <v>171</v>
+      </c>
+      <c r="D26" t="s">
         <v>172</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>173</v>
-      </c>
-      <c r="E26" t="s">
-        <v>174</v>
       </c>
       <c r="F26" t="s">
         <v>77</v>
       </c>
       <c r="G26" t="s">
+        <v>174</v>
+      </c>
+      <c r="H26" t="s">
         <v>175</v>
-      </c>
-      <c r="H26" t="s">
-        <v>176</v>
       </c>
       <c r="I26" t="s">
         <v>15</v>
       </c>
       <c r="J26" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="K26" t="s">
+        <v>176</v>
+      </c>
+      <c r="L26" t="s">
         <v>177</v>
-      </c>
-      <c r="L26" t="s">
-        <v>178</v>
       </c>
       <c r="M26" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>46081</v>
       </c>
       <c r="B27" t="s">
+        <v>178</v>
+      </c>
+      <c r="C27" t="s">
+        <v>171</v>
+      </c>
+      <c r="D27" t="s">
+        <v>142</v>
+      </c>
+      <c r="E27" t="s">
         <v>179</v>
       </c>
-      <c r="C27" t="s">
-        <v>172</v>
-      </c>
-      <c r="D27" t="s">
-        <v>143</v>
-      </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>180</v>
       </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
         <v>181</v>
       </c>
-      <c r="G27" t="s">
+      <c r="H27" t="s">
         <v>182</v>
       </c>
-      <c r="H27" t="s">
+      <c r="I27" t="s">
         <v>183</v>
       </c>
-      <c r="I27" t="s">
+      <c r="J27" t="s">
         <v>184</v>
       </c>
-      <c r="J27" t="s">
+      <c r="K27" t="s">
         <v>185</v>
       </c>
-      <c r="K27" t="s">
+      <c r="L27" t="s">
         <v>186</v>
       </c>
-      <c r="L27" t="s">
+      <c r="M27" t="s">
         <v>187</v>
       </c>
-      <c r="M27" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>46082</v>
       </c>
       <c r="B28" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C28" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D28" t="s">
+        <v>190</v>
+      </c>
+      <c r="E28" t="s">
+        <v>181</v>
+      </c>
+      <c r="F28" t="s">
+        <v>180</v>
+      </c>
+      <c r="G28" t="s">
         <v>191</v>
       </c>
-      <c r="E28" t="s">
-        <v>182</v>
-      </c>
-      <c r="F28" t="s">
-        <v>181</v>
-      </c>
-      <c r="G28" t="s">
+      <c r="H28" t="s">
         <v>192</v>
       </c>
-      <c r="H28" t="s">
+      <c r="I28" t="s">
         <v>193</v>
       </c>
-      <c r="I28" t="s">
+      <c r="J28" t="s">
         <v>194</v>
       </c>
-      <c r="J28" t="s">
+      <c r="K28" t="s">
         <v>195</v>
       </c>
-      <c r="K28" t="s">
+      <c r="L28" t="s">
         <v>196</v>
       </c>
-      <c r="L28" t="s">
+      <c r="M28" t="s">
         <v>197</v>
       </c>
-      <c r="M28" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>46082</v>
       </c>
       <c r="B29" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C29" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D29" t="s">
         <v>16</v>
       </c>
       <c r="E29" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F29" t="s">
+        <v>198</v>
+      </c>
+      <c r="G29" t="s">
         <v>199</v>
       </c>
-      <c r="G29" t="s">
+      <c r="H29" t="s">
         <v>200</v>
       </c>
-      <c r="H29" t="s">
-        <v>201</v>
-      </c>
       <c r="I29" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J29" t="s">
         <v>15</v>
       </c>
       <c r="K29" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L29" t="s">
         <v>24</v>
       </c>
       <c r="M29" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>46088</v>
       </c>
       <c r="B30" t="s">
+        <v>203</v>
+      </c>
+      <c r="C30" t="s">
+        <v>171</v>
+      </c>
+      <c r="D30" t="s">
         <v>204</v>
       </c>
-      <c r="C30" t="s">
-        <v>172</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
+        <v>142</v>
+      </c>
+      <c r="F30" t="s">
+        <v>115</v>
+      </c>
+      <c r="G30" t="s">
+        <v>190</v>
+      </c>
+      <c r="H30" t="s">
         <v>205</v>
       </c>
-      <c r="E30" t="s">
-        <v>143</v>
-      </c>
-      <c r="F30" t="s">
-        <v>116</v>
-      </c>
-      <c r="G30" t="s">
-        <v>191</v>
-      </c>
-      <c r="H30" t="s">
-        <v>206</v>
-      </c>
       <c r="I30" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J30" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K30" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="L30" t="s">
         <v>28</v>
       </c>
       <c r="M30" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>46089</v>
       </c>
       <c r="B31" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C31" t="s">
         <v>0</v>
@@ -2391,13 +2388,13 @@
         <v>24</v>
       </c>
       <c r="E31" t="s">
+        <v>208</v>
+      </c>
+      <c r="F31" t="s">
         <v>209</v>
       </c>
-      <c r="F31" t="s">
+      <c r="G31" t="s">
         <v>210</v>
-      </c>
-      <c r="G31" t="s">
-        <v>211</v>
       </c>
       <c r="H31" t="s">
         <v>64</v>
@@ -2406,106 +2403,106 @@
         <v>41</v>
       </c>
       <c r="J31" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K31" t="s">
+        <v>211</v>
+      </c>
+      <c r="L31" t="s">
         <v>212</v>
       </c>
-      <c r="L31" t="s">
+      <c r="M31" t="s">
         <v>213</v>
       </c>
-      <c r="M31" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>46090</v>
       </c>
       <c r="B32" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C32" t="s">
         <v>0</v>
       </c>
       <c r="D32" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E32" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F32" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G32" t="s">
         <v>78</v>
       </c>
       <c r="H32" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I32" t="s">
+        <v>216</v>
+      </c>
+      <c r="J32" t="s">
         <v>217</v>
       </c>
-      <c r="J32" t="s">
-        <v>218</v>
-      </c>
       <c r="K32" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="L32" t="s">
         <v>90</v>
       </c>
       <c r="M32" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>46091</v>
       </c>
       <c r="B33" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C33" t="s">
         <v>1</v>
       </c>
       <c r="D33" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E33" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F33" t="s">
         <v>89</v>
       </c>
       <c r="G33" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H33" t="s">
+        <v>219</v>
+      </c>
+      <c r="I33" t="s">
+        <v>147</v>
+      </c>
+      <c r="J33" t="s">
         <v>220</v>
-      </c>
-      <c r="I33" t="s">
-        <v>148</v>
-      </c>
-      <c r="J33" t="s">
-        <v>221</v>
       </c>
       <c r="K33" t="s">
         <v>28</v>
       </c>
       <c r="L33" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M33" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>46092</v>
       </c>
       <c r="B34" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C34" t="s">
         <v>43</v>
@@ -2514,236 +2511,236 @@
         <v>15</v>
       </c>
       <c r="E34" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F34" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G34" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H34" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I34" t="s">
         <v>17</v>
       </c>
       <c r="J34" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K34" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="L34" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M34" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>46092</v>
       </c>
       <c r="B35" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C35" t="s">
         <v>51</v>
       </c>
       <c r="D35" t="s">
+        <v>222</v>
+      </c>
+      <c r="E35" t="s">
         <v>223</v>
       </c>
-      <c r="E35" t="s">
+      <c r="F35" t="s">
+        <v>173</v>
+      </c>
+      <c r="G35" t="s">
         <v>224</v>
       </c>
-      <c r="F35" t="s">
-        <v>174</v>
-      </c>
-      <c r="G35" t="s">
+      <c r="H35" t="s">
         <v>225</v>
       </c>
-      <c r="H35" t="s">
-        <v>226</v>
-      </c>
       <c r="I35" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J35" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K35" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="L35" t="s">
         <v>41</v>
       </c>
       <c r="M35" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>46093</v>
       </c>
       <c r="B36" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C36" t="s">
         <v>51</v>
       </c>
       <c r="D36" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E36" t="s">
         <v>89</v>
       </c>
       <c r="F36" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G36" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H36" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I36" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="J36" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="K36" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L36" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="M36" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>46093</v>
       </c>
       <c r="B37" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C37" t="s">
         <v>55</v>
       </c>
       <c r="D37" t="s">
+        <v>222</v>
+      </c>
+      <c r="E37" t="s">
+        <v>229</v>
+      </c>
+      <c r="F37" t="s">
+        <v>116</v>
+      </c>
+      <c r="G37" t="s">
+        <v>180</v>
+      </c>
+      <c r="H37" t="s">
+        <v>230</v>
+      </c>
+      <c r="I37" t="s">
         <v>223</v>
       </c>
-      <c r="E37" t="s">
-        <v>230</v>
-      </c>
-      <c r="F37" t="s">
-        <v>117</v>
-      </c>
-      <c r="G37" t="s">
-        <v>181</v>
-      </c>
-      <c r="H37" t="s">
+      <c r="J37" t="s">
+        <v>149</v>
+      </c>
+      <c r="K37" t="s">
+        <v>225</v>
+      </c>
+      <c r="L37" t="s">
         <v>231</v>
       </c>
-      <c r="I37" t="s">
-        <v>224</v>
-      </c>
-      <c r="J37" t="s">
-        <v>150</v>
-      </c>
-      <c r="K37" t="s">
+      <c r="M37" t="s">
         <v>226</v>
       </c>
-      <c r="L37" t="s">
-        <v>232</v>
-      </c>
-      <c r="M37" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>46094</v>
       </c>
       <c r="B38" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C38" t="s">
         <v>55</v>
       </c>
       <c r="D38" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E38" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F38" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G38" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H38" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I38" t="s">
         <v>89</v>
       </c>
       <c r="J38" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K38" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L38" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="M38" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>46094</v>
       </c>
       <c r="B39" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C39" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D39" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E39" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F39" t="s">
+        <v>234</v>
+      </c>
+      <c r="G39" t="s">
         <v>235</v>
       </c>
-      <c r="G39" t="s">
-        <v>236</v>
-      </c>
       <c r="H39" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I39" t="s">
         <v>37</v>
       </c>
       <c r="J39" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K39" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L39" t="s">
         <v>68</v>
       </c>
       <c r="M39" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
   </sheetData>

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Desktop/Fantasy Cycling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="54" documentId="13_ncr:1_{8C193552-8267-4083-B3AB-168CA7CCEC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BCF866F3-633D-4351-911C-7771EA164932}"/>
+  <xr:revisionPtr revIDLastSave="58" documentId="13_ncr:1_{8C193552-8267-4083-B3AB-168CA7CCEC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{677EC544-502C-48E6-8953-FBCE48C65D8C}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{D48BDCD1-ADE3-4EE7-A9DB-3C7F51FF7246}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D48BDCD1-ADE3-4EE7-A9DB-3C7F51FF7246}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="238">
   <si>
     <t>Stage 1</t>
   </si>
@@ -750,6 +750,9 @@
   </si>
   <si>
     <t>Alex Baudin</t>
+  </si>
+  <si>
+    <t>Jasper Stuyven</t>
   </si>
 </sst>
 </file>
@@ -1128,23 +1131,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6820EB03-3F7F-49BA-9E92-28FA32BF7E1D}">
-  <dimension ref="A1:M39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M41"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="20.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="27" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="27" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.5546875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>42</v>
       </c>
@@ -1185,7 +1188,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>46042</v>
       </c>
@@ -1226,7 +1229,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>46043</v>
       </c>
@@ -1267,7 +1270,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>46044</v>
       </c>
@@ -1308,7 +1311,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>46045</v>
       </c>
@@ -1349,7 +1352,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>46046</v>
       </c>
@@ -1390,7 +1393,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>46047</v>
       </c>
@@ -1431,7 +1434,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>46054</v>
       </c>
@@ -1472,7 +1475,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>46057</v>
       </c>
@@ -1513,7 +1516,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>46058</v>
       </c>
@@ -1554,7 +1557,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>46059</v>
       </c>
@@ -1595,7 +1598,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>46060</v>
       </c>
@@ -1636,7 +1639,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>46061</v>
       </c>
@@ -1677,7 +1680,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>46069</v>
       </c>
@@ -1718,7 +1721,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>46070</v>
       </c>
@@ -1759,7 +1762,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>46071</v>
       </c>
@@ -1800,7 +1803,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>46071</v>
       </c>
@@ -1841,7 +1844,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>46072</v>
       </c>
@@ -1882,7 +1885,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>46072</v>
       </c>
@@ -1923,7 +1926,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>46073</v>
       </c>
@@ -1964,7 +1967,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>46073</v>
       </c>
@@ -2005,7 +2008,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>46074</v>
       </c>
@@ -2046,7 +2049,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>46074</v>
       </c>
@@ -2087,7 +2090,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>46075</v>
       </c>
@@ -2128,7 +2131,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>46075</v>
       </c>
@@ -2169,7 +2172,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>46081</v>
       </c>
@@ -2210,7 +2213,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>46081</v>
       </c>
@@ -2251,7 +2254,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>46082</v>
       </c>
@@ -2292,7 +2295,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>46082</v>
       </c>
@@ -2333,7 +2336,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>46088</v>
       </c>
@@ -2374,7 +2377,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>46089</v>
       </c>
@@ -2415,7 +2418,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>46090</v>
       </c>
@@ -2456,7 +2459,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>46091</v>
       </c>
@@ -2497,7 +2500,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>46092</v>
       </c>
@@ -2538,7 +2541,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>46092</v>
       </c>
@@ -2579,7 +2582,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>46093</v>
       </c>
@@ -2620,7 +2623,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>46093</v>
       </c>
@@ -2661,7 +2664,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>46094</v>
       </c>
@@ -2702,7 +2705,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>46094</v>
       </c>
@@ -2741,6 +2744,88 @@
       </c>
       <c r="M39" t="s">
         <v>236</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
+        <v>46095</v>
+      </c>
+      <c r="B40" t="s">
+        <v>207</v>
+      </c>
+      <c r="C40" t="s">
+        <v>162</v>
+      </c>
+      <c r="D40" t="s">
+        <v>193</v>
+      </c>
+      <c r="E40" t="s">
+        <v>64</v>
+      </c>
+      <c r="F40" t="s">
+        <v>100</v>
+      </c>
+      <c r="G40" t="s">
+        <v>37</v>
+      </c>
+      <c r="H40" t="s">
+        <v>24</v>
+      </c>
+      <c r="I40" t="s">
+        <v>200</v>
+      </c>
+      <c r="J40" t="s">
+        <v>41</v>
+      </c>
+      <c r="K40" t="s">
+        <v>237</v>
+      </c>
+      <c r="L40" t="s">
+        <v>198</v>
+      </c>
+      <c r="M40" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
+        <v>46095</v>
+      </c>
+      <c r="B41" t="s">
+        <v>214</v>
+      </c>
+      <c r="C41" t="s">
+        <v>158</v>
+      </c>
+      <c r="D41" t="s">
+        <v>115</v>
+      </c>
+      <c r="E41" t="s">
+        <v>106</v>
+      </c>
+      <c r="F41" t="s">
+        <v>181</v>
+      </c>
+      <c r="G41" t="s">
+        <v>89</v>
+      </c>
+      <c r="H41" t="s">
+        <v>220</v>
+      </c>
+      <c r="I41" t="s">
+        <v>233</v>
+      </c>
+      <c r="J41" t="s">
+        <v>228</v>
+      </c>
+      <c r="K41" t="s">
+        <v>78</v>
+      </c>
+      <c r="L41" t="s">
+        <v>217</v>
+      </c>
+      <c r="M41" t="s">
+        <v>219</v>
       </c>
     </row>
   </sheetData>

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Desktop/Fantasy Cycling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="58" documentId="13_ncr:1_{8C193552-8267-4083-B3AB-168CA7CCEC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{677EC544-502C-48E6-8953-FBCE48C65D8C}"/>
+  <xr:revisionPtr revIDLastSave="64" documentId="13_ncr:1_{8C193552-8267-4083-B3AB-168CA7CCEC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5DFFCBD8-2985-4937-A755-93CDC6893589}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D48BDCD1-ADE3-4EE7-A9DB-3C7F51FF7246}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="242">
   <si>
     <t>Stage 1</t>
   </si>
@@ -753,6 +753,18 @@
   </si>
   <si>
     <t>Jasper Stuyven</t>
+  </si>
+  <si>
+    <t>Nicolas Vinokurov</t>
+  </si>
+  <si>
+    <t>Anders Foldager</t>
+  </si>
+  <si>
+    <t>Stage 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stage 7 </t>
   </si>
 </sst>
 </file>
@@ -1131,7 +1143,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6820EB03-3F7F-49BA-9E92-28FA32BF7E1D}">
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
@@ -2828,6 +2840,88 @@
         <v>219</v>
       </c>
     </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A42" s="1">
+        <v>46096</v>
+      </c>
+      <c r="B42" t="s">
+        <v>207</v>
+      </c>
+      <c r="C42" t="s">
+        <v>240</v>
+      </c>
+      <c r="D42" t="s">
+        <v>180</v>
+      </c>
+      <c r="E42" t="s">
+        <v>222</v>
+      </c>
+      <c r="F42" t="s">
+        <v>116</v>
+      </c>
+      <c r="G42" t="s">
+        <v>149</v>
+      </c>
+      <c r="H42" t="s">
+        <v>236</v>
+      </c>
+      <c r="I42" t="s">
+        <v>225</v>
+      </c>
+      <c r="J42" t="s">
+        <v>230</v>
+      </c>
+      <c r="K42" t="s">
+        <v>231</v>
+      </c>
+      <c r="L42" t="s">
+        <v>238</v>
+      </c>
+      <c r="M42" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A43" s="1">
+        <v>46096</v>
+      </c>
+      <c r="B43" t="s">
+        <v>214</v>
+      </c>
+      <c r="C43" t="s">
+        <v>241</v>
+      </c>
+      <c r="D43" t="s">
+        <v>130</v>
+      </c>
+      <c r="E43" t="s">
+        <v>17</v>
+      </c>
+      <c r="F43" t="s">
+        <v>202</v>
+      </c>
+      <c r="G43" t="s">
+        <v>128</v>
+      </c>
+      <c r="H43" t="s">
+        <v>122</v>
+      </c>
+      <c r="I43" t="s">
+        <v>15</v>
+      </c>
+      <c r="J43" t="s">
+        <v>239</v>
+      </c>
+      <c r="K43" t="s">
+        <v>124</v>
+      </c>
+      <c r="L43" t="s">
+        <v>66</v>
+      </c>
+      <c r="M43" t="s">
+        <v>227</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M20" xr:uid="{6820EB03-3F7F-49BA-9E92-28FA32BF7E1D}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M25">
